--- a/011_Can_SapAriba_Paramount_Dispatcher/Data/CanSapAribaParamountDispatcherConfig.xlsx
+++ b/011_Can_SapAriba_Paramount_Dispatcher/Data/CanSapAribaParamountDispatcherConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://insidemedia-my.sharepoint.com/personal/forms_membership__nycgrm_ar_service_groupm_com/Documents/Desktop/Aniket Code/Paramount/011_Can_SapAriba_Paramount_Dispatcher/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{B464C772-0EF5-4002-9488-2DA611DCFF9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{031260CA-A212-415D-B7A3-47F1BF09F357}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{B464C772-0EF5-4002-9488-2DA611DCFF9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2B33C62-3795-405E-A8E3-A8BFD3C7CDC5}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="8745" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -121,9 +121,6 @@
     <t>SMEs</t>
   </si>
   <si>
-    <t>aniketni@cybage.com</t>
-  </si>
-  <si>
     <t>Email Html Values</t>
   </si>
   <si>
@@ -302,6 +299,9 @@
   </si>
   <si>
     <t>SharePoint subfolder</t>
+  </si>
+  <si>
+    <t>aniketni@cybage.com;</t>
   </si>
 </sst>
 </file>
@@ -359,7 +359,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -370,6 +370,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -385,10 +386,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -826,38 +823,38 @@
       <c r="A16" t="s">
         <v>25</v>
       </c>
-      <c r="B16" t="s">
-        <v>26</v>
+      <c r="B16" s="6" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="18" spans="1:2" ht="14.25" customHeight="1">
       <c r="A18" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="14.25" customHeight="1">
       <c r="A19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" t="s">
         <v>28</v>
-      </c>
-      <c r="B19" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="14.25" customHeight="1">
       <c r="A20" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" t="s">
         <v>30</v>
-      </c>
-      <c r="B20" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="14.25" customHeight="1">
       <c r="A21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="14.25" customHeight="1"/>
@@ -1837,11 +1834,8 @@
     <row r="996" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
-  <hyperlinks>
-    <hyperlink ref="B16" r:id="rId1" xr:uid="{ACB2BA46-96D6-40BC-8794-BAFEED114C41}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1892,138 +1886,138 @@
     </row>
     <row r="2" spans="1:26" ht="30">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="45">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="5" spans="1:26" ht="14.25" customHeight="1">
       <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s">
         <v>38</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>39</v>
-      </c>
-      <c r="C5" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
         <v>41</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>42</v>
-      </c>
-      <c r="C7" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
       <c r="A8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" t="s">
         <v>44</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>45</v>
-      </c>
-      <c r="C8" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
       <c r="A9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" t="s">
         <v>47</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>48</v>
-      </c>
-      <c r="C9" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1">
       <c r="A10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" t="s">
         <v>50</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>51</v>
-      </c>
-      <c r="C10" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1">
       <c r="A11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" t="s">
         <v>53</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>54</v>
-      </c>
-      <c r="C11" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1">
       <c r="A12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" t="s">
         <v>56</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>57</v>
-      </c>
-      <c r="C12" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="14" spans="1:26" ht="14.25" customHeight="1">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
       <c r="A15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="17" spans="1:3" ht="45">
       <c r="A17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B17" t="b">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1"/>
@@ -3019,13 +3013,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -3052,86 +3046,86 @@
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1">
       <c r="A2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" t="s">
         <v>68</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>69</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>70</v>
-      </c>
-      <c r="D2" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1">
       <c r="A3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" t="s">
         <v>72</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" t="s">
         <v>73</v>
-      </c>
-      <c r="C3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D3" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1">
       <c r="A4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" t="s">
         <v>75</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" t="s">
         <v>76</v>
-      </c>
-      <c r="C4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D4" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1">
       <c r="A5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" t="s">
         <v>78</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D5" t="s">
         <v>79</v>
-      </c>
-      <c r="C5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D5" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1">
       <c r="A6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" t="s">
         <v>81</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" t="s">
         <v>82</v>
-      </c>
-      <c r="C6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" t="s">
         <v>84</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" t="s">
         <v>85</v>
-      </c>
-      <c r="C7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D7" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1"/>
@@ -4133,12 +4127,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="7f25b792-b2ba-4b5c-8669-b39a27555406" xsi:nil="true"/>
+    <Time xmlns="649a79cd-06e4-47a3-aac9-21cb806f3675" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="649a79cd-06e4-47a3-aac9-21cb806f3675">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4377,21 +4374,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="7f25b792-b2ba-4b5c-8669-b39a27555406" xsi:nil="true"/>
-    <Time xmlns="649a79cd-06e4-47a3-aac9-21cb806f3675" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="649a79cd-06e4-47a3-aac9-21cb806f3675">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1451EC1E-2FC7-45C1-A096-CF2F1D99CEA7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{267B89B1-EC80-4460-B457-5C0CB7C26FA6}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="7f25b792-b2ba-4b5c-8669-b39a27555406"/>
+    <ds:schemaRef ds:uri="649a79cd-06e4-47a3-aac9-21cb806f3675"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4416,12 +4413,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{267B89B1-EC80-4460-B457-5C0CB7C26FA6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1451EC1E-2FC7-45C1-A096-CF2F1D99CEA7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="7f25b792-b2ba-4b5c-8669-b39a27555406"/>
-    <ds:schemaRef ds:uri="649a79cd-06e4-47a3-aac9-21cb806f3675"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/011_Can_SapAriba_Paramount_Dispatcher/Data/CanSapAribaParamountDispatcherConfig.xlsx
+++ b/011_Can_SapAriba_Paramount_Dispatcher/Data/CanSapAribaParamountDispatcherConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://insidemedia-my.sharepoint.com/personal/forms_membership__nycgrm_ar_service_groupm_com/Documents/Desktop/Aniket Code/Paramount/011_Can_SapAriba_Paramount_Dispatcher/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{B464C772-0EF5-4002-9488-2DA611DCFF9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2B33C62-3795-405E-A8E3-A8BFD3C7CDC5}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{B464C772-0EF5-4002-9488-2DA611DCFF9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8638FB44-C067-4AB0-86E2-AFEDFB07A1CC}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="8745" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -301,7 +301,7 @@
     <t>SharePoint subfolder</t>
   </si>
   <si>
-    <t>aniketni@cybage.com;</t>
+    <t>aniketni@cybage.com;rohitpaw@cybage.com</t>
   </si>
 </sst>
 </file>
@@ -386,6 +386,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4127,15 +4131,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="7f25b792-b2ba-4b5c-8669-b39a27555406" xsi:nil="true"/>
-    <Time xmlns="649a79cd-06e4-47a3-aac9-21cb806f3675" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="649a79cd-06e4-47a3-aac9-21cb806f3675">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4374,21 +4375,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="7f25b792-b2ba-4b5c-8669-b39a27555406" xsi:nil="true"/>
+    <Time xmlns="649a79cd-06e4-47a3-aac9-21cb806f3675" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="649a79cd-06e4-47a3-aac9-21cb806f3675">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{267B89B1-EC80-4460-B457-5C0CB7C26FA6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1451EC1E-2FC7-45C1-A096-CF2F1D99CEA7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="7f25b792-b2ba-4b5c-8669-b39a27555406"/>
-    <ds:schemaRef ds:uri="649a79cd-06e4-47a3-aac9-21cb806f3675"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4413,9 +4414,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1451EC1E-2FC7-45C1-A096-CF2F1D99CEA7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{267B89B1-EC80-4460-B457-5C0CB7C26FA6}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="7f25b792-b2ba-4b5c-8669-b39a27555406"/>
+    <ds:schemaRef ds:uri="649a79cd-06e4-47a3-aac9-21cb806f3675"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>